--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592235</v>
+        <v>121592227</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594284</v>
+        <v>594269</v>
       </c>
       <c r="R2" t="n">
-        <v>7184808</v>
+        <v>7185009</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592233</v>
+        <v>121592185</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594352</v>
+        <v>594049</v>
       </c>
       <c r="R3" t="n">
-        <v>7184890</v>
+        <v>7184999</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592228</v>
+        <v>121592224</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1036,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594268</v>
+        <v>594089</v>
       </c>
       <c r="R5" t="n">
-        <v>7185009</v>
+        <v>7185081</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592224</v>
+        <v>121592228</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594089</v>
+        <v>594268</v>
       </c>
       <c r="R6" t="n">
-        <v>7185081</v>
+        <v>7185009</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592226</v>
+        <v>121592233</v>
       </c>
       <c r="B7" t="n">
-        <v>74715</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594243</v>
+        <v>594352</v>
       </c>
       <c r="R7" t="n">
-        <v>7185027</v>
+        <v>7184890</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592230</v>
+        <v>121592223</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,26 +1377,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1400,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594286</v>
+        <v>594064</v>
       </c>
       <c r="R8" t="n">
-        <v>7185013</v>
+        <v>7185153</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592229</v>
+        <v>121592235</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594285</v>
+        <v>594284</v>
       </c>
       <c r="R9" t="n">
-        <v>7185014</v>
+        <v>7184808</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592185</v>
+        <v>121592231</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1625,7 +1626,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594049</v>
+        <v>594351</v>
       </c>
       <c r="R10" t="n">
-        <v>7184999</v>
+        <v>7184984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592225</v>
+        <v>121592226</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>74715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1723,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594132</v>
+        <v>594243</v>
       </c>
       <c r="R11" t="n">
-        <v>7185047</v>
+        <v>7185027</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592227</v>
+        <v>121592229</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,34 +1835,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594269</v>
+        <v>594285</v>
       </c>
       <c r="R12" t="n">
-        <v>7185009</v>
+        <v>7185014</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592223</v>
+        <v>121592225</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1980,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594064</v>
+        <v>594132</v>
       </c>
       <c r="R13" t="n">
-        <v>7185153</v>
+        <v>7185047</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592231</v>
+        <v>121592234</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,39 +2069,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594351</v>
+        <v>594353</v>
       </c>
       <c r="R14" t="n">
-        <v>7184984</v>
+        <v>7184895</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592234</v>
+        <v>121592230</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,34 +2181,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594353</v>
+        <v>594286</v>
       </c>
       <c r="R15" t="n">
-        <v>7184895</v>
+        <v>7185013</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592227</v>
+        <v>121592223</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594269</v>
+        <v>594064</v>
       </c>
       <c r="R2" t="n">
-        <v>7185009</v>
+        <v>7185153</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592185</v>
+        <v>121592236</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,10 +825,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594049</v>
+        <v>594241</v>
       </c>
       <c r="R3" t="n">
-        <v>7184999</v>
+        <v>7184750</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592236</v>
+        <v>121592224</v>
       </c>
       <c r="B4" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,9 +941,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594241</v>
+        <v>594089</v>
       </c>
       <c r="R4" t="n">
-        <v>7184750</v>
+        <v>7185081</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592224</v>
+        <v>121592234</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594089</v>
+        <v>594353</v>
       </c>
       <c r="R5" t="n">
-        <v>7185081</v>
+        <v>7184895</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592228</v>
+        <v>121592225</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594268</v>
+        <v>594132</v>
       </c>
       <c r="R6" t="n">
-        <v>7185009</v>
+        <v>7185047</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592223</v>
+        <v>121592229</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1397,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594064</v>
+        <v>594285</v>
       </c>
       <c r="R8" t="n">
-        <v>7185153</v>
+        <v>7185014</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592231</v>
+        <v>121592185</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1626,7 +1631,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1635,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594351</v>
+        <v>594049</v>
       </c>
       <c r="R10" t="n">
-        <v>7184984</v>
+        <v>7184999</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592226</v>
+        <v>121592228</v>
       </c>
       <c r="B11" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1728,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594243</v>
+        <v>594268</v>
       </c>
       <c r="R11" t="n">
-        <v>7185027</v>
+        <v>7185009</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592229</v>
+        <v>121592227</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1840,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594285</v>
+        <v>594269</v>
       </c>
       <c r="R12" t="n">
-        <v>7185014</v>
+        <v>7185009</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592225</v>
+        <v>121592230</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,27 +1952,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1981,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594132</v>
+        <v>594286</v>
       </c>
       <c r="R13" t="n">
-        <v>7185047</v>
+        <v>7185013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592234</v>
+        <v>121592226</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594353</v>
+        <v>594243</v>
       </c>
       <c r="R14" t="n">
-        <v>7184895</v>
+        <v>7185027</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592230</v>
+        <v>121592231</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,26 +2180,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594286</v>
+        <v>594351</v>
       </c>
       <c r="R15" t="n">
-        <v>7185013</v>
+        <v>7184984</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592223</v>
+        <v>121592231</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594064</v>
+        <v>594351</v>
       </c>
       <c r="R2" t="n">
-        <v>7185153</v>
+        <v>7184984</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592236</v>
+        <v>121592229</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,9 +825,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594241</v>
+        <v>594285</v>
       </c>
       <c r="R3" t="n">
-        <v>7184750</v>
+        <v>7185014</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592224</v>
+        <v>121592234</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594089</v>
+        <v>594353</v>
       </c>
       <c r="R4" t="n">
-        <v>7185081</v>
+        <v>7184895</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592234</v>
+        <v>121592223</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594353</v>
+        <v>594064</v>
       </c>
       <c r="R5" t="n">
-        <v>7184895</v>
+        <v>7185153</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592225</v>
+        <v>121592233</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594132</v>
+        <v>594352</v>
       </c>
       <c r="R6" t="n">
-        <v>7185047</v>
+        <v>7184890</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592233</v>
+        <v>121592224</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594352</v>
+        <v>594089</v>
       </c>
       <c r="R7" t="n">
-        <v>7184890</v>
+        <v>7185081</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592229</v>
+        <v>121592185</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1411,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594285</v>
+        <v>594049</v>
       </c>
       <c r="R8" t="n">
-        <v>7185014</v>
+        <v>7184999</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592235</v>
+        <v>121592226</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594284</v>
+        <v>594243</v>
       </c>
       <c r="R9" t="n">
-        <v>7184808</v>
+        <v>7185027</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592185</v>
+        <v>121592235</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594049</v>
+        <v>594284</v>
       </c>
       <c r="R10" t="n">
-        <v>7184999</v>
+        <v>7184808</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592228</v>
+        <v>121592236</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1724,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594268</v>
+        <v>594241</v>
       </c>
       <c r="R11" t="n">
-        <v>7185009</v>
+        <v>7184750</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592230</v>
+        <v>121592225</v>
       </c>
       <c r="B13" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,26 +1952,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1980,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594286</v>
+        <v>594132</v>
       </c>
       <c r="R13" t="n">
-        <v>7185013</v>
+        <v>7185047</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592226</v>
+        <v>121592228</v>
       </c>
       <c r="B14" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,21 +2069,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594243</v>
+        <v>594268</v>
       </c>
       <c r="R14" t="n">
-        <v>7185027</v>
+        <v>7185009</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592231</v>
+        <v>121592230</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,27 +2181,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594351</v>
+        <v>594286</v>
       </c>
       <c r="R15" t="n">
-        <v>7184984</v>
+        <v>7185013</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592231</v>
+        <v>121592234</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594351</v>
+        <v>594353</v>
       </c>
       <c r="R2" t="n">
-        <v>7184984</v>
+        <v>7184895</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592229</v>
+        <v>121592224</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -828,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594285</v>
+        <v>594089</v>
       </c>
       <c r="R3" t="n">
-        <v>7185014</v>
+        <v>7185081</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592234</v>
+        <v>121592227</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594353</v>
+        <v>594269</v>
       </c>
       <c r="R4" t="n">
-        <v>7184895</v>
+        <v>7185009</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592223</v>
+        <v>121592233</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594064</v>
+        <v>594352</v>
       </c>
       <c r="R5" t="n">
-        <v>7185153</v>
+        <v>7184890</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592233</v>
+        <v>121592225</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594352</v>
+        <v>594132</v>
       </c>
       <c r="R6" t="n">
-        <v>7184890</v>
+        <v>7185047</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592224</v>
+        <v>121592230</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,27 +1261,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594089</v>
+        <v>594286</v>
       </c>
       <c r="R7" t="n">
-        <v>7185081</v>
+        <v>7185013</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592226</v>
+        <v>121592223</v>
       </c>
       <c r="B9" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594243</v>
+        <v>594064</v>
       </c>
       <c r="R9" t="n">
-        <v>7185027</v>
+        <v>7185153</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592235</v>
+        <v>121592229</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1611,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594284</v>
+        <v>594285</v>
       </c>
       <c r="R10" t="n">
-        <v>7184808</v>
+        <v>7185014</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592236</v>
+        <v>121592235</v>
       </c>
       <c r="B11" t="n">
-        <v>56560</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,38 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594241</v>
+        <v>594284</v>
       </c>
       <c r="R11" t="n">
-        <v>7184750</v>
+        <v>7184808</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592227</v>
+        <v>121592236</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>56560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,34 +1840,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594269</v>
+        <v>594241</v>
       </c>
       <c r="R12" t="n">
-        <v>7185009</v>
+        <v>7184750</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592225</v>
+        <v>121592231</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1981,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594132</v>
+        <v>594351</v>
       </c>
       <c r="R13" t="n">
-        <v>7185047</v>
+        <v>7184984</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2165,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592230</v>
+        <v>121592226</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>74715</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2185,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594286</v>
+        <v>594243</v>
       </c>
       <c r="R15" t="n">
-        <v>7185013</v>
+        <v>7185027</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592235</v>
+        <v>121592236</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1728,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594284</v>
+        <v>594241</v>
       </c>
       <c r="R11" t="n">
-        <v>7184808</v>
+        <v>7184750</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592236</v>
+        <v>121592235</v>
       </c>
       <c r="B12" t="n">
-        <v>56560</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594241</v>
+        <v>594284</v>
       </c>
       <c r="R12" t="n">
-        <v>7184750</v>
+        <v>7184808</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592226</v>
+        <v>121592185</v>
       </c>
       <c r="B2" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594243</v>
+        <v>594049</v>
       </c>
       <c r="R2" t="n">
-        <v>7185027</v>
+        <v>7184999</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592229</v>
+        <v>121592227</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594285</v>
+        <v>594269</v>
       </c>
       <c r="R3" t="n">
-        <v>7185014</v>
+        <v>7185009</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592228</v>
+        <v>121592234</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594268</v>
+        <v>594353</v>
       </c>
       <c r="R4" t="n">
-        <v>7185009</v>
+        <v>7184895</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592224</v>
+        <v>121592228</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594089</v>
+        <v>594268</v>
       </c>
       <c r="R5" t="n">
-        <v>7185081</v>
+        <v>7185009</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592231</v>
+        <v>121592230</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,27 +1144,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594351</v>
+        <v>594286</v>
       </c>
       <c r="R6" t="n">
-        <v>7184984</v>
+        <v>7185013</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592223</v>
+        <v>121592236</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1400,10 +1394,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594064</v>
+        <v>594241</v>
       </c>
       <c r="R8" t="n">
-        <v>7185153</v>
+        <v>7184750</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592230</v>
+        <v>121592223</v>
       </c>
       <c r="B9" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,26 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594286</v>
+        <v>594064</v>
       </c>
       <c r="R9" t="n">
-        <v>7185013</v>
+        <v>7185153</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1594,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592185</v>
+        <v>121592229</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1645,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594049</v>
+        <v>594285</v>
       </c>
       <c r="R10" t="n">
-        <v>7184999</v>
+        <v>7185014</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592235</v>
+        <v>121592226</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,21 +1727,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1757,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594284</v>
+        <v>594243</v>
       </c>
       <c r="R11" t="n">
-        <v>7184808</v>
+        <v>7185027</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592233</v>
+        <v>121592231</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,34 +1839,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594352</v>
+        <v>594351</v>
       </c>
       <c r="R12" t="n">
-        <v>7184890</v>
+        <v>7184984</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592227</v>
+        <v>121592224</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1956,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594269</v>
+        <v>594089</v>
       </c>
       <c r="R13" t="n">
-        <v>7185009</v>
+        <v>7185081</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592234</v>
+        <v>121592233</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,21 +2073,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594353</v>
+        <v>594352</v>
       </c>
       <c r="R14" t="n">
-        <v>7184895</v>
+        <v>7184890</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2165,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592236</v>
+        <v>121592235</v>
       </c>
       <c r="B15" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2185,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594241</v>
+        <v>594284</v>
       </c>
       <c r="R15" t="n">
-        <v>7184750</v>
+        <v>7184808</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592185</v>
+        <v>121592223</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594049</v>
+        <v>594064</v>
       </c>
       <c r="R2" t="n">
-        <v>7184999</v>
+        <v>7185153</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592227</v>
+        <v>121592224</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594269</v>
+        <v>594089</v>
       </c>
       <c r="R3" t="n">
-        <v>7185009</v>
+        <v>7185081</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592234</v>
+        <v>121592227</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594353</v>
+        <v>594269</v>
       </c>
       <c r="R4" t="n">
-        <v>7184895</v>
+        <v>7185009</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592228</v>
+        <v>121592229</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594268</v>
+        <v>594285</v>
       </c>
       <c r="R5" t="n">
-        <v>7185009</v>
+        <v>7185014</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592230</v>
+        <v>121592226</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>74722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594286</v>
+        <v>594243</v>
       </c>
       <c r="R6" t="n">
-        <v>7185013</v>
+        <v>7185027</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592225</v>
+        <v>121592235</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594132</v>
+        <v>594284</v>
       </c>
       <c r="R7" t="n">
-        <v>7185047</v>
+        <v>7184808</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592236</v>
+        <v>121592231</v>
       </c>
       <c r="B8" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,16 +1378,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1394,9 +1395,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1405,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594241</v>
+        <v>594351</v>
       </c>
       <c r="R8" t="n">
-        <v>7184750</v>
+        <v>7184984</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592223</v>
+        <v>121592225</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1522,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594064</v>
+        <v>594132</v>
       </c>
       <c r="R9" t="n">
-        <v>7185153</v>
+        <v>7185047</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592229</v>
+        <v>121592236</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,16 +1612,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,10 +1629,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1639,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594285</v>
+        <v>594241</v>
       </c>
       <c r="R10" t="n">
-        <v>7185014</v>
+        <v>7184750</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592226</v>
+        <v>121592185</v>
       </c>
       <c r="B11" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,34 +1728,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594243</v>
+        <v>594049</v>
       </c>
       <c r="R11" t="n">
-        <v>7185027</v>
+        <v>7184999</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592231</v>
+        <v>121592233</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,39 +1845,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594351</v>
+        <v>594352</v>
       </c>
       <c r="R12" t="n">
-        <v>7184984</v>
+        <v>7184890</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592224</v>
+        <v>121592230</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,27 +1957,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594089</v>
+        <v>594286</v>
       </c>
       <c r="R13" t="n">
-        <v>7185081</v>
+        <v>7185013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592233</v>
+        <v>121592234</v>
       </c>
       <c r="B14" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594352</v>
+        <v>594353</v>
       </c>
       <c r="R14" t="n">
-        <v>7184890</v>
+        <v>7184895</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592235</v>
+        <v>121592228</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594284</v>
+        <v>594268</v>
       </c>
       <c r="R15" t="n">
-        <v>7184808</v>
+        <v>7185009</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592223</v>
+        <v>121592227</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594064</v>
+        <v>594269</v>
       </c>
       <c r="R2" t="n">
-        <v>7185153</v>
+        <v>7185009</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592224</v>
+        <v>121592225</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594089</v>
+        <v>594132</v>
       </c>
       <c r="R3" t="n">
-        <v>7185081</v>
+        <v>7185047</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592227</v>
+        <v>121592185</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594269</v>
+        <v>594049</v>
       </c>
       <c r="R4" t="n">
-        <v>7185009</v>
+        <v>7184999</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592229</v>
+        <v>121592223</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594285</v>
+        <v>594064</v>
       </c>
       <c r="R5" t="n">
-        <v>7185014</v>
+        <v>7185153</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592226</v>
+        <v>121592230</v>
       </c>
       <c r="B6" t="n">
-        <v>74722</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594243</v>
+        <v>594286</v>
       </c>
       <c r="R6" t="n">
-        <v>7185027</v>
+        <v>7185013</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1479,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592225</v>
+        <v>121592233</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594132</v>
+        <v>594352</v>
       </c>
       <c r="R9" t="n">
-        <v>7185047</v>
+        <v>7184890</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592236</v>
+        <v>121592226</v>
       </c>
       <c r="B10" t="n">
-        <v>56561</v>
+        <v>74722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,38 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594241</v>
+        <v>594243</v>
       </c>
       <c r="R10" t="n">
-        <v>7184750</v>
+        <v>7185027</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592185</v>
+        <v>121592224</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1748,7 +1743,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1757,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594049</v>
+        <v>594089</v>
       </c>
       <c r="R11" t="n">
-        <v>7184999</v>
+        <v>7185081</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592233</v>
+        <v>121592229</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,34 +1840,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594352</v>
+        <v>594285</v>
       </c>
       <c r="R12" t="n">
-        <v>7184890</v>
+        <v>7185014</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592230</v>
+        <v>121592236</v>
       </c>
       <c r="B13" t="n">
-        <v>57510</v>
+        <v>56561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594286</v>
+        <v>594241</v>
       </c>
       <c r="R13" t="n">
-        <v>7185013</v>
+        <v>7184750</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,7 +2057,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592234</v>
+        <v>121592228</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594353</v>
+        <v>594268</v>
       </c>
       <c r="R14" t="n">
-        <v>7184895</v>
+        <v>7185009</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,7 +2169,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592228</v>
+        <v>121592234</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594268</v>
+        <v>594353</v>
       </c>
       <c r="R15" t="n">
-        <v>7185009</v>
+        <v>7184895</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592227</v>
+        <v>121592233</v>
       </c>
       <c r="B2" t="n">
         <v>90746</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594269</v>
+        <v>594352</v>
       </c>
       <c r="R2" t="n">
-        <v>7185009</v>
+        <v>7184890</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592225</v>
+        <v>121592235</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594132</v>
+        <v>594284</v>
       </c>
       <c r="R3" t="n">
-        <v>7185047</v>
+        <v>7184808</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592185</v>
+        <v>121592226</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594049</v>
+        <v>594243</v>
       </c>
       <c r="R4" t="n">
-        <v>7184999</v>
+        <v>7185027</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592223</v>
+        <v>121592227</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594064</v>
+        <v>594269</v>
       </c>
       <c r="R5" t="n">
-        <v>7185153</v>
+        <v>7185009</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592230</v>
+        <v>121592225</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,26 +1139,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594286</v>
+        <v>594132</v>
       </c>
       <c r="R6" t="n">
-        <v>7185013</v>
+        <v>7185047</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592235</v>
+        <v>121592231</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594284</v>
+        <v>594351</v>
       </c>
       <c r="R7" t="n">
-        <v>7184808</v>
+        <v>7184984</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592231</v>
+        <v>121592224</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1411,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594351</v>
+        <v>594089</v>
       </c>
       <c r="R8" t="n">
-        <v>7184984</v>
+        <v>7185081</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592233</v>
+        <v>121592228</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594352</v>
+        <v>594268</v>
       </c>
       <c r="R9" t="n">
-        <v>7184890</v>
+        <v>7185009</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592226</v>
+        <v>121592229</v>
       </c>
       <c r="B10" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594243</v>
+        <v>594285</v>
       </c>
       <c r="R10" t="n">
-        <v>7185027</v>
+        <v>7185014</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592224</v>
+        <v>121592234</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594089</v>
+        <v>594353</v>
       </c>
       <c r="R11" t="n">
-        <v>7185081</v>
+        <v>7184895</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592229</v>
+        <v>121592185</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1869,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594285</v>
+        <v>594049</v>
       </c>
       <c r="R12" t="n">
-        <v>7185014</v>
+        <v>7184999</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592236</v>
+        <v>121592223</v>
       </c>
       <c r="B13" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,16 +1948,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,9 +1965,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594241</v>
+        <v>594064</v>
       </c>
       <c r="R13" t="n">
-        <v>7184750</v>
+        <v>7185153</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2020,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592228</v>
+        <v>121592236</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,34 +2065,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594268</v>
+        <v>594241</v>
       </c>
       <c r="R14" t="n">
-        <v>7185009</v>
+        <v>7184750</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592234</v>
+        <v>121592230</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,34 +2181,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594353</v>
+        <v>594286</v>
       </c>
       <c r="R15" t="n">
-        <v>7184895</v>
+        <v>7185013</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592233</v>
+        <v>121592229</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594352</v>
+        <v>594285</v>
       </c>
       <c r="R2" t="n">
-        <v>7184890</v>
+        <v>7185014</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592226</v>
+        <v>121592224</v>
       </c>
       <c r="B4" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594243</v>
+        <v>594089</v>
       </c>
       <c r="R4" t="n">
-        <v>7185027</v>
+        <v>7185081</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592227</v>
+        <v>121592225</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594269</v>
+        <v>594132</v>
       </c>
       <c r="R5" t="n">
-        <v>7185009</v>
+        <v>7185047</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592225</v>
+        <v>121592231</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1168,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594132</v>
+        <v>594351</v>
       </c>
       <c r="R6" t="n">
-        <v>7185047</v>
+        <v>7184984</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592231</v>
+        <v>121592226</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>74722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594351</v>
+        <v>594243</v>
       </c>
       <c r="R7" t="n">
-        <v>7184984</v>
+        <v>7185027</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592224</v>
+        <v>121592185</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1393,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594089</v>
+        <v>594049</v>
       </c>
       <c r="R8" t="n">
-        <v>7185081</v>
+        <v>7184999</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592228</v>
+        <v>121592234</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1514,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594268</v>
+        <v>594353</v>
       </c>
       <c r="R9" t="n">
-        <v>7185009</v>
+        <v>7184895</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592229</v>
+        <v>121592230</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1612,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594285</v>
+        <v>594286</v>
       </c>
       <c r="R10" t="n">
-        <v>7185014</v>
+        <v>7185013</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592234</v>
+        <v>121592228</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1743,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594353</v>
+        <v>594268</v>
       </c>
       <c r="R11" t="n">
-        <v>7184895</v>
+        <v>7185009</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592185</v>
+        <v>121592236</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,16 +1840,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,10 +1857,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1860,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594049</v>
+        <v>594241</v>
       </c>
       <c r="R12" t="n">
-        <v>7184999</v>
+        <v>7184750</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592223</v>
+        <v>121592227</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,39 +1956,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594064</v>
+        <v>594269</v>
       </c>
       <c r="R13" t="n">
-        <v>7185153</v>
+        <v>7185009</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592236</v>
+        <v>121592223</v>
       </c>
       <c r="B14" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,16 +2068,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2082,9 +2085,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2093,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594241</v>
+        <v>594064</v>
       </c>
       <c r="R14" t="n">
-        <v>7184750</v>
+        <v>7185153</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2128,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592230</v>
+        <v>121592233</v>
       </c>
       <c r="B15" t="n">
-        <v>57510</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,38 +2185,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594286</v>
+        <v>594352</v>
       </c>
       <c r="R15" t="n">
-        <v>7185013</v>
+        <v>7184890</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592229</v>
+        <v>121592225</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594285</v>
+        <v>594132</v>
       </c>
       <c r="R2" t="n">
-        <v>7185014</v>
+        <v>7185047</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592235</v>
+        <v>121592185</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594284</v>
+        <v>594049</v>
       </c>
       <c r="R3" t="n">
-        <v>7184808</v>
+        <v>7184999</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592224</v>
+        <v>121592235</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594089</v>
+        <v>594284</v>
       </c>
       <c r="R4" t="n">
-        <v>7185081</v>
+        <v>7184808</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592225</v>
+        <v>121592227</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594132</v>
+        <v>594269</v>
       </c>
       <c r="R5" t="n">
-        <v>7185047</v>
+        <v>7185009</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592231</v>
+        <v>121592230</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,27 +1149,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594351</v>
+        <v>594286</v>
       </c>
       <c r="R6" t="n">
-        <v>7184984</v>
+        <v>7185013</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592226</v>
+        <v>121592233</v>
       </c>
       <c r="B7" t="n">
-        <v>74722</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594243</v>
+        <v>594352</v>
       </c>
       <c r="R7" t="n">
-        <v>7185027</v>
+        <v>7184890</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592185</v>
+        <v>121592229</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1412,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594049</v>
+        <v>594285</v>
       </c>
       <c r="R8" t="n">
-        <v>7184999</v>
+        <v>7185014</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592234</v>
+        <v>121592236</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1494,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594353</v>
+        <v>594241</v>
       </c>
       <c r="R9" t="n">
-        <v>7184895</v>
+        <v>7184750</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592230</v>
+        <v>121592234</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,38 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594286</v>
+        <v>594353</v>
       </c>
       <c r="R10" t="n">
-        <v>7185013</v>
+        <v>7184895</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592228</v>
+        <v>121592223</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1722,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594268</v>
+        <v>594064</v>
       </c>
       <c r="R11" t="n">
-        <v>7185009</v>
+        <v>7185153</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592236</v>
+        <v>121592228</v>
       </c>
       <c r="B12" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1839,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594241</v>
+        <v>594268</v>
       </c>
       <c r="R12" t="n">
-        <v>7184750</v>
+        <v>7185009</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592227</v>
+        <v>121592226</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
+        <v>74722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594269</v>
+        <v>594243</v>
       </c>
       <c r="R13" t="n">
-        <v>7185009</v>
+        <v>7185027</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,7 +2047,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592223</v>
+        <v>121592224</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2097,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594064</v>
+        <v>594089</v>
       </c>
       <c r="R14" t="n">
-        <v>7185153</v>
+        <v>7185081</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592233</v>
+        <v>121592231</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,34 +2180,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594352</v>
+        <v>594351</v>
       </c>
       <c r="R15" t="n">
-        <v>7184890</v>
+        <v>7184984</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592225</v>
+        <v>121592228</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594132</v>
+        <v>594268</v>
       </c>
       <c r="R2" t="n">
-        <v>7185047</v>
+        <v>7185009</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592185</v>
+        <v>121592223</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594049</v>
+        <v>594064</v>
       </c>
       <c r="R3" t="n">
-        <v>7184999</v>
+        <v>7185153</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592235</v>
+        <v>121592224</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594284</v>
+        <v>594089</v>
       </c>
       <c r="R4" t="n">
-        <v>7184808</v>
+        <v>7185081</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592227</v>
+        <v>121592229</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594269</v>
+        <v>594285</v>
       </c>
       <c r="R5" t="n">
-        <v>7185009</v>
+        <v>7185014</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592230</v>
+        <v>121592233</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>90760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594286</v>
+        <v>594352</v>
       </c>
       <c r="R6" t="n">
-        <v>7185013</v>
+        <v>7184890</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592233</v>
+        <v>121592236</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1266,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594352</v>
+        <v>594241</v>
       </c>
       <c r="R7" t="n">
-        <v>7184890</v>
+        <v>7184750</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592229</v>
+        <v>121592231</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594285</v>
+        <v>594351</v>
       </c>
       <c r="R8" t="n">
-        <v>7185014</v>
+        <v>7184984</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592236</v>
+        <v>121592234</v>
       </c>
       <c r="B9" t="n">
-        <v>56561</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594241</v>
+        <v>594353</v>
       </c>
       <c r="R9" t="n">
-        <v>7184750</v>
+        <v>7184895</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592234</v>
+        <v>121592227</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594353</v>
+        <v>594269</v>
       </c>
       <c r="R10" t="n">
-        <v>7184895</v>
+        <v>7185009</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592223</v>
+        <v>121592185</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,7 +1743,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594064</v>
+        <v>594049</v>
       </c>
       <c r="R11" t="n">
-        <v>7185153</v>
+        <v>7184999</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592228</v>
+        <v>121592235</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594268</v>
+        <v>594284</v>
       </c>
       <c r="R12" t="n">
-        <v>7185009</v>
+        <v>7184808</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592226</v>
+        <v>121592230</v>
       </c>
       <c r="B13" t="n">
-        <v>74722</v>
+        <v>57518</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,34 +1952,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594243</v>
+        <v>594286</v>
       </c>
       <c r="R13" t="n">
-        <v>7185027</v>
+        <v>7185013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592224</v>
+        <v>121592226</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>74735</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,39 +2068,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594089</v>
+        <v>594243</v>
       </c>
       <c r="R14" t="n">
-        <v>7185081</v>
+        <v>7185027</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592231</v>
+        <v>121592225</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594351</v>
+        <v>594132</v>
       </c>
       <c r="R15" t="n">
-        <v>7184984</v>
+        <v>7185047</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 44874-2024 artfynd.xlsx
+++ b/artfynd/A 44874-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121592228</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -787,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592223</v>
+        <v>121592234</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594064</v>
+        <v>594353</v>
       </c>
       <c r="R3" t="n">
-        <v>7185153</v>
+        <v>7184895</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592224</v>
+        <v>121592235</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594089</v>
+        <v>594284</v>
       </c>
       <c r="R4" t="n">
-        <v>7185081</v>
+        <v>7184808</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592229</v>
+        <v>121592226</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594285</v>
+        <v>594243</v>
       </c>
       <c r="R5" t="n">
-        <v>7185014</v>
+        <v>7185027</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592233</v>
+        <v>1994934</v>
       </c>
       <c r="B6" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bullersjön, Ås lm</t>
+          <t>V om Ulvoberg, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594352</v>
+        <v>594324</v>
       </c>
       <c r="R6" t="n">
-        <v>7184890</v>
+        <v>7185028</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,31 +1184,39 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592236</v>
+        <v>121592185</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,16 +1224,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1283,9 +1241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594241</v>
+        <v>594049</v>
       </c>
       <c r="R7" t="n">
-        <v>7184750</v>
+        <v>7184999</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,15 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592231</v>
+        <v>121592223</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594351</v>
+        <v>594064</v>
       </c>
       <c r="R8" t="n">
-        <v>7184984</v>
+        <v>7185153</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,15 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592234</v>
+        <v>121592224</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,34 +1448,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594353</v>
+        <v>594089</v>
       </c>
       <c r="R9" t="n">
-        <v>7184895</v>
+        <v>7185081</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1512,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,15 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592227</v>
+        <v>121592225</v>
       </c>
       <c r="B10" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,34 +1560,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594269</v>
+        <v>594132</v>
       </c>
       <c r="R10" t="n">
-        <v>7185009</v>
+        <v>7185047</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,15 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592185</v>
+        <v>121592229</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594049</v>
+        <v>594285</v>
       </c>
       <c r="R11" t="n">
-        <v>7184999</v>
+        <v>7185014</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,15 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592235</v>
+        <v>121592231</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,34 +1784,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594284</v>
+        <v>594351</v>
       </c>
       <c r="R12" t="n">
-        <v>7184808</v>
+        <v>7184984</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,37 +1885,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592230</v>
+        <v>121592236</v>
       </c>
       <c r="B13" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1980,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594286</v>
+        <v>594241</v>
       </c>
       <c r="R13" t="n">
-        <v>7185013</v>
+        <v>7184750</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2015,7 +1959,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +1969,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,15 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592226</v>
+        <v>121592230</v>
       </c>
       <c r="B14" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,34 +2007,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594243</v>
+        <v>594286</v>
       </c>
       <c r="R14" t="n">
-        <v>7185027</v>
+        <v>7185013</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,7 +2070,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2080,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,123 +2104,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121592225</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>594132</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7185047</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
